--- a/artfynd/A 61033-2023 artfynd.xlsx
+++ b/artfynd/A 61033-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1304,6 +1304,2787 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>132612503</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79341</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hambågamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>759285</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7165516</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>132613335</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91855</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hambågamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>759476</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7165646</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>132612527</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91842</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>112</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Stjärntagging</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Asterodon ferruginosus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hambågamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>759259</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7165528</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>132613655</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80326</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hambågamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>759705</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7165475</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>på stammen av äldre asp</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>132612134</v>
+      </c>
+      <c r="B12" t="n">
+        <v>83163</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hambågamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>759624</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7165409</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>132612190</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57961</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hambågamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>759605</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7165415</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>påbörjat bohål?</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>132613364</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57945</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hambågamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>759701</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7165535</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>hål hackat i basen på en gran</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>132612240</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57948</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hambågamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>759575</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7165402</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>132612586</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57948</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hambågamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>759275</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7165618</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>132613617</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79317</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Hambågamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>759716</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7165500</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>132613720</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57948</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hambågamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>759791</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7165487</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>132612091</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57948</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hambågamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>759624</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7165409</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>132613541</v>
+      </c>
+      <c r="B20" t="n">
+        <v>83163</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Hambågamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>759750</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7165501</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>132613549</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79317</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Hambågamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>759750</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7165501</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>132613777</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57945</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Hambågamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>759822</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7165468</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>hål hackade i låga</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>132613579</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57945</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Hambågamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>759771</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7165491</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>hack i död ved</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>132612369</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91913</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Hambågamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>759530</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7165474</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>132612549</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57945</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Hambågamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>759273</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7165552</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>hål hackat i träd</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>132613808</v>
+      </c>
+      <c r="B26" t="n">
+        <v>91892</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Hambågamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>759830</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7165467</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>132613756</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57945</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Hambågamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>759795</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7165475</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>många hål hackade i gran</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>132613674</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57961</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Hambågamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>759705</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7165475</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>påbörjat litet bohål i asp</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>132613644</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57945</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Hambågamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>759714</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7165461</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>hål hackade i ihålig asp</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>132611890</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79341</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Hambågamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>759627</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7165400</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>132612433</v>
+      </c>
+      <c r="B31" t="n">
+        <v>83163</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Hambågamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>759308</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7165476</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>132612321</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57945</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Hambågamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>759567</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7165410</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>hål hackat i gran</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>132611969</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57948</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Hambågamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>759627</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7165400</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61033-2023 artfynd.xlsx
+++ b/artfynd/A 61033-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132500773</v>
       </c>
       <c r="B2" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>132500548</v>
       </c>
       <c r="B3" t="n">
-        <v>58109</v>
+        <v>58110</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>132500379</v>
       </c>
       <c r="B4" t="n">
-        <v>91913</v>
+        <v>91919</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>132500492</v>
       </c>
       <c r="B5" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>132500598</v>
       </c>
       <c r="B6" t="n">
-        <v>57136</v>
+        <v>57137</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>132500854</v>
       </c>
       <c r="B7" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>132612503</v>
       </c>
       <c r="B8" t="n">
-        <v>79341</v>
+        <v>79343</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1411,10 +1411,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132613335</v>
+        <v>132613655</v>
       </c>
       <c r="B9" t="n">
-        <v>91855</v>
+        <v>80328</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1422,27 +1422,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>6456</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>759476</v>
+        <v>759705</v>
       </c>
       <c r="R9" t="n">
-        <v>7165646</v>
+        <v>7165475</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,6 +1489,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>på stammen av äldre asp</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1519,7 +1524,7 @@
         <v>132612527</v>
       </c>
       <c r="B10" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1621,10 +1626,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132613655</v>
+        <v>132613335</v>
       </c>
       <c r="B11" t="n">
-        <v>80326</v>
+        <v>91861</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1632,27 +1637,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1663,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>759705</v>
+        <v>759476</v>
       </c>
       <c r="R11" t="n">
-        <v>7165475</v>
+        <v>7165646</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,11 +1704,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>på stammen av äldre asp</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1734,7 +1734,7 @@
         <v>132612134</v>
       </c>
       <c r="B12" t="n">
-        <v>83163</v>
+        <v>83165</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>132612190</v>
       </c>
       <c r="B13" t="n">
-        <v>57961</v>
+        <v>57962</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>132613364</v>
       </c>
       <c r="B14" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>132612240</v>
       </c>
       <c r="B15" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2158,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132612586</v>
+        <v>132613617</v>
       </c>
       <c r="B16" t="n">
-        <v>57948</v>
+        <v>79319</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2169,31 +2169,30 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2201,10 +2200,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>759275</v>
+        <v>759716</v>
       </c>
       <c r="R16" t="n">
-        <v>7165618</v>
+        <v>7165500</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2239,17 +2238,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2268,10 +2263,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132613617</v>
+        <v>132612586</v>
       </c>
       <c r="B17" t="n">
-        <v>79317</v>
+        <v>57949</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2279,30 +2274,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2310,10 +2306,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>759716</v>
+        <v>759275</v>
       </c>
       <c r="R17" t="n">
-        <v>7165500</v>
+        <v>7165618</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2348,13 +2344,17 @@
           <t>2026-04-17</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2376,7 +2376,7 @@
         <v>132613720</v>
       </c>
       <c r="B18" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>132612091</v>
       </c>
       <c r="B19" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2585,10 +2585,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132613541</v>
+        <v>132613549</v>
       </c>
       <c r="B20" t="n">
-        <v>83163</v>
+        <v>79319</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2596,27 +2596,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -2690,10 +2690,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132613549</v>
+        <v>132613541</v>
       </c>
       <c r="B21" t="n">
-        <v>79317</v>
+        <v>83165</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2701,27 +2701,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -2798,7 +2798,7 @@
         <v>132613777</v>
       </c>
       <c r="B22" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>132613579</v>
       </c>
       <c r="B23" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3015,10 +3015,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132612369</v>
+        <v>132613808</v>
       </c>
       <c r="B24" t="n">
-        <v>91913</v>
+        <v>91898</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3026,21 +3026,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>759530</v>
+        <v>759830</v>
       </c>
       <c r="R24" t="n">
-        <v>7165474</v>
+        <v>7165467</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3120,10 +3120,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132612549</v>
+        <v>132612369</v>
       </c>
       <c r="B25" t="n">
-        <v>57945</v>
+        <v>91919</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3131,31 +3131,30 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3163,10 +3162,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>759273</v>
+        <v>759530</v>
       </c>
       <c r="R25" t="n">
-        <v>7165552</v>
+        <v>7165474</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3201,17 +3200,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>hål hackat i träd</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3230,10 +3225,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132613808</v>
+        <v>132612549</v>
       </c>
       <c r="B26" t="n">
-        <v>91892</v>
+        <v>57946</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3241,30 +3236,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3272,10 +3268,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>759830</v>
+        <v>759273</v>
       </c>
       <c r="R26" t="n">
-        <v>7165467</v>
+        <v>7165552</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3310,13 +3306,17 @@
           <t>2026-04-17</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>hål hackat i träd</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3338,7 +3338,7 @@
         <v>132613756</v>
       </c>
       <c r="B27" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>132613674</v>
       </c>
       <c r="B28" t="n">
-        <v>57961</v>
+        <v>57962</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3551,42 +3551,41 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132613644</v>
+        <v>132611890</v>
       </c>
       <c r="B29" t="n">
-        <v>57945</v>
+        <v>79343</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6434</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3594,10 +3593,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>759714</v>
+        <v>759627</v>
       </c>
       <c r="R29" t="n">
-        <v>7165461</v>
+        <v>7165400</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3632,17 +3631,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>hål hackade i ihålig asp</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3661,38 +3656,38 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132611890</v>
+        <v>132612433</v>
       </c>
       <c r="B30" t="n">
-        <v>79341</v>
+        <v>83165</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6434</v>
+        <v>1312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -3703,10 +3698,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>759627</v>
+        <v>759308</v>
       </c>
       <c r="R30" t="n">
-        <v>7165400</v>
+        <v>7165476</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3766,10 +3761,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132612433</v>
+        <v>132612321</v>
       </c>
       <c r="B31" t="n">
-        <v>83163</v>
+        <v>57946</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3777,30 +3772,31 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3808,10 +3804,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>759308</v>
+        <v>759567</v>
       </c>
       <c r="R31" t="n">
-        <v>7165476</v>
+        <v>7165410</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3846,13 +3842,17 @@
           <t>2026-04-17</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>hål hackat i gran</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3871,10 +3871,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132612321</v>
+        <v>132613644</v>
       </c>
       <c r="B32" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3914,10 +3914,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>759567</v>
+        <v>759714</v>
       </c>
       <c r="R32" t="n">
-        <v>7165410</v>
+        <v>7165461</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>hål hackat i gran</t>
+          <t>hål hackade i ihålig asp</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3984,7 +3984,7 @@
         <v>132611969</v>
       </c>
       <c r="B33" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 61033-2023 artfynd.xlsx
+++ b/artfynd/A 61033-2023 artfynd.xlsx
@@ -1411,38 +1411,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132613655</v>
+        <v>132612527</v>
       </c>
       <c r="B9" t="n">
-        <v>80328</v>
+        <v>91848</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>112</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>759705</v>
+        <v>759259</v>
       </c>
       <c r="R9" t="n">
-        <v>7165475</v>
+        <v>7165528</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,11 +1489,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>på stammen av äldre asp</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,32 +1516,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132612527</v>
+        <v>132613335</v>
       </c>
       <c r="B10" t="n">
-        <v>91848</v>
+        <v>91861</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>112</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1558,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>759259</v>
+        <v>759476</v>
       </c>
       <c r="R10" t="n">
-        <v>7165528</v>
+        <v>7165646</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1626,10 +1621,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132613335</v>
+        <v>132613655</v>
       </c>
       <c r="B11" t="n">
-        <v>91861</v>
+        <v>80328</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1637,27 +1632,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1668,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>759476</v>
+        <v>759705</v>
       </c>
       <c r="R11" t="n">
-        <v>7165646</v>
+        <v>7165475</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,6 +1699,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>på stammen av äldre asp</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1942,10 +1942,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132613364</v>
+        <v>132612240</v>
       </c>
       <c r="B14" t="n">
-        <v>57946</v>
+        <v>57949</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1953,16 +1953,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1973,11 +1973,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1985,10 +1981,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>759701</v>
+        <v>759575</v>
       </c>
       <c r="R14" t="n">
-        <v>7165535</v>
+        <v>7165402</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2025,14 +2021,14 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>hål hackat i basen på en gran</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG14" t="b">
         <v>0</v>
@@ -2052,10 +2048,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132612240</v>
+        <v>132613364</v>
       </c>
       <c r="B15" t="n">
-        <v>57949</v>
+        <v>57946</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2063,16 +2059,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2083,7 +2079,11 @@
       <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>759575</v>
+        <v>759701</v>
       </c>
       <c r="R15" t="n">
-        <v>7165402</v>
+        <v>7165535</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2131,14 +2131,14 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>hål hackat i basen på en gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="b">
         <v>0</v>

--- a/artfynd/A 61033-2023 artfynd.xlsx
+++ b/artfynd/A 61033-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132500773</v>
       </c>
       <c r="B2" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>132500548</v>
       </c>
       <c r="B3" t="n">
-        <v>58110</v>
+        <v>58114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>132500379</v>
       </c>
       <c r="B4" t="n">
-        <v>91919</v>
+        <v>91929</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>132500492</v>
       </c>
       <c r="B5" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>132500598</v>
       </c>
       <c r="B6" t="n">
-        <v>57137</v>
+        <v>57141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>132500854</v>
       </c>
       <c r="B7" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>132612503</v>
       </c>
       <c r="B8" t="n">
-        <v>79343</v>
+        <v>79351</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1411,38 +1411,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132612527</v>
+        <v>132613655</v>
       </c>
       <c r="B9" t="n">
-        <v>91848</v>
+        <v>80336</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>112</v>
+        <v>6456</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>759259</v>
+        <v>759705</v>
       </c>
       <c r="R9" t="n">
-        <v>7165528</v>
+        <v>7165475</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,6 +1489,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>på stammen av äldre asp</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,32 +1521,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132613335</v>
+        <v>132612527</v>
       </c>
       <c r="B10" t="n">
-        <v>91861</v>
+        <v>91858</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>112</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1558,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>759476</v>
+        <v>759259</v>
       </c>
       <c r="R10" t="n">
-        <v>7165646</v>
+        <v>7165528</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1621,10 +1626,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132613655</v>
+        <v>132613335</v>
       </c>
       <c r="B11" t="n">
-        <v>80328</v>
+        <v>91871</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1632,27 +1637,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1663,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>759705</v>
+        <v>759476</v>
       </c>
       <c r="R11" t="n">
-        <v>7165475</v>
+        <v>7165646</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,11 +1704,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>på stammen av äldre asp</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1734,7 +1734,7 @@
         <v>132612134</v>
       </c>
       <c r="B12" t="n">
-        <v>83165</v>
+        <v>83173</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>132612190</v>
       </c>
       <c r="B13" t="n">
-        <v>57962</v>
+        <v>57966</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>132612240</v>
       </c>
       <c r="B14" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         <v>132613364</v>
       </c>
       <c r="B15" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2158,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132613617</v>
+        <v>132612586</v>
       </c>
       <c r="B16" t="n">
-        <v>79319</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2169,30 +2169,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2200,10 +2201,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>759716</v>
+        <v>759275</v>
       </c>
       <c r="R16" t="n">
-        <v>7165500</v>
+        <v>7165618</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2238,13 +2239,17 @@
           <t>2026-04-17</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2263,10 +2268,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132612586</v>
+        <v>132613617</v>
       </c>
       <c r="B17" t="n">
-        <v>57949</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2274,31 +2279,30 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2306,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>759275</v>
+        <v>759716</v>
       </c>
       <c r="R17" t="n">
-        <v>7165618</v>
+        <v>7165500</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2344,17 +2348,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2376,7 +2376,7 @@
         <v>132613720</v>
       </c>
       <c r="B18" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>132612091</v>
       </c>
       <c r="B19" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2585,10 +2585,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132613549</v>
+        <v>132613541</v>
       </c>
       <c r="B20" t="n">
-        <v>79319</v>
+        <v>83173</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2596,27 +2596,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -2690,10 +2690,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132613541</v>
+        <v>132613549</v>
       </c>
       <c r="B21" t="n">
-        <v>83165</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2701,27 +2701,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -2798,7 +2798,7 @@
         <v>132613777</v>
       </c>
       <c r="B22" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>132613579</v>
       </c>
       <c r="B23" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>132613808</v>
       </c>
       <c r="B24" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>132612369</v>
       </c>
       <c r="B25" t="n">
-        <v>91919</v>
+        <v>91929</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>132612549</v>
       </c>
       <c r="B26" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         <v>132613756</v>
       </c>
       <c r="B27" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>132613674</v>
       </c>
       <c r="B28" t="n">
-        <v>57962</v>
+        <v>57966</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>132611890</v>
       </c>
       <c r="B29" t="n">
-        <v>79343</v>
+        <v>79351</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>132612433</v>
       </c>
       <c r="B30" t="n">
-        <v>83165</v>
+        <v>83173</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>132612321</v>
       </c>
       <c r="B31" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>132613644</v>
       </c>
       <c r="B32" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>132611969</v>
       </c>
       <c r="B33" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 61033-2023 artfynd.xlsx
+++ b/artfynd/A 61033-2023 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>132500379</v>
       </c>
       <c r="B4" t="n">
-        <v>91929</v>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>132500492</v>
       </c>
       <c r="B5" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1411,10 +1411,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132613655</v>
+        <v>132613335</v>
       </c>
       <c r="B9" t="n">
-        <v>80336</v>
+        <v>91872</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1422,27 +1422,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>759705</v>
+        <v>759476</v>
       </c>
       <c r="R9" t="n">
-        <v>7165475</v>
+        <v>7165646</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,11 +1489,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>på stammen av äldre asp</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1524,7 +1519,7 @@
         <v>132612527</v>
       </c>
       <c r="B10" t="n">
-        <v>91858</v>
+        <v>91859</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,10 +1621,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132613335</v>
+        <v>132613655</v>
       </c>
       <c r="B11" t="n">
-        <v>91871</v>
+        <v>80336</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1637,27 +1632,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1668,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>759476</v>
+        <v>759705</v>
       </c>
       <c r="R11" t="n">
-        <v>7165646</v>
+        <v>7165475</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,6 +1699,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>på stammen av äldre asp</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2158,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132612586</v>
+        <v>132613617</v>
       </c>
       <c r="B16" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2169,31 +2169,30 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2201,10 +2200,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>759275</v>
+        <v>759716</v>
       </c>
       <c r="R16" t="n">
-        <v>7165618</v>
+        <v>7165500</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2239,17 +2238,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2268,10 +2263,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132613617</v>
+        <v>132612586</v>
       </c>
       <c r="B17" t="n">
-        <v>79327</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2279,30 +2274,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2310,10 +2306,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>759716</v>
+        <v>759275</v>
       </c>
       <c r="R17" t="n">
-        <v>7165500</v>
+        <v>7165618</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2348,13 +2344,17 @@
           <t>2026-04-17</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -3018,7 +3018,7 @@
         <v>132613808</v>
       </c>
       <c r="B24" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>132612369</v>
       </c>
       <c r="B25" t="n">
-        <v>91929</v>
+        <v>91930</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3551,41 +3551,42 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132611890</v>
+        <v>132612321</v>
       </c>
       <c r="B29" t="n">
-        <v>79351</v>
+        <v>57950</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6434</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3593,10 +3594,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>759627</v>
+        <v>759567</v>
       </c>
       <c r="R29" t="n">
-        <v>7165400</v>
+        <v>7165410</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3631,13 +3632,17 @@
           <t>2026-04-17</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>hål hackat i gran</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3656,10 +3661,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132612433</v>
+        <v>132613644</v>
       </c>
       <c r="B30" t="n">
-        <v>83173</v>
+        <v>57950</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3667,30 +3672,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3698,10 +3704,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>759308</v>
+        <v>759714</v>
       </c>
       <c r="R30" t="n">
-        <v>7165476</v>
+        <v>7165461</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3736,13 +3742,17 @@
           <t>2026-04-17</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>hål hackade i ihålig asp</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3761,10 +3771,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132612321</v>
+        <v>132612433</v>
       </c>
       <c r="B31" t="n">
-        <v>57950</v>
+        <v>83173</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3772,31 +3782,30 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3804,10 +3813,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>759567</v>
+        <v>759308</v>
       </c>
       <c r="R31" t="n">
-        <v>7165410</v>
+        <v>7165476</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3842,17 +3851,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>hål hackat i gran</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3871,42 +3876,41 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132613644</v>
+        <v>132611890</v>
       </c>
       <c r="B32" t="n">
-        <v>57950</v>
+        <v>79351</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6434</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3914,10 +3918,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>759714</v>
+        <v>759627</v>
       </c>
       <c r="R32" t="n">
-        <v>7165461</v>
+        <v>7165400</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3952,17 +3956,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>hål hackade i ihålig asp</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 61033-2023 artfynd.xlsx
+++ b/artfynd/A 61033-2023 artfynd.xlsx
@@ -993,7 +993,7 @@
         <v>132500492</v>
       </c>
       <c r="B5" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1516,38 +1516,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132612527</v>
+        <v>132613655</v>
       </c>
       <c r="B10" t="n">
-        <v>91859</v>
+        <v>80336</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>112</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1558,10 +1558,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>759259</v>
+        <v>759705</v>
       </c>
       <c r="R10" t="n">
-        <v>7165528</v>
+        <v>7165475</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1594,6 +1594,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>på stammen av äldre asp</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1621,38 +1626,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132613655</v>
+        <v>132612527</v>
       </c>
       <c r="B11" t="n">
-        <v>80336</v>
+        <v>91859</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>112</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1663,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>759705</v>
+        <v>759259</v>
       </c>
       <c r="R11" t="n">
-        <v>7165475</v>
+        <v>7165528</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,11 +1704,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>på stammen av äldre asp</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2585,10 +2585,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132613541</v>
+        <v>132613549</v>
       </c>
       <c r="B20" t="n">
-        <v>83173</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2596,27 +2596,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -2690,10 +2690,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132613549</v>
+        <v>132613541</v>
       </c>
       <c r="B21" t="n">
-        <v>79327</v>
+        <v>83173</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2701,27 +2701,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -3551,10 +3551,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132612321</v>
+        <v>132612433</v>
       </c>
       <c r="B29" t="n">
-        <v>57950</v>
+        <v>83173</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3562,31 +3562,30 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3594,10 +3593,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>759567</v>
+        <v>759308</v>
       </c>
       <c r="R29" t="n">
-        <v>7165410</v>
+        <v>7165476</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3632,17 +3631,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>hål hackat i gran</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3661,42 +3656,41 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132613644</v>
+        <v>132611890</v>
       </c>
       <c r="B30" t="n">
-        <v>57950</v>
+        <v>79351</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6434</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3704,10 +3698,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>759714</v>
+        <v>759627</v>
       </c>
       <c r="R30" t="n">
-        <v>7165461</v>
+        <v>7165400</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3742,17 +3736,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>hål hackade i ihålig asp</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3771,10 +3761,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132612433</v>
+        <v>132613644</v>
       </c>
       <c r="B31" t="n">
-        <v>83173</v>
+        <v>57950</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3782,30 +3772,31 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3813,10 +3804,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>759308</v>
+        <v>759714</v>
       </c>
       <c r="R31" t="n">
-        <v>7165476</v>
+        <v>7165461</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3851,13 +3842,17 @@
           <t>2026-04-17</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>hål hackade i ihålig asp</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3876,41 +3871,42 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132611890</v>
+        <v>132612321</v>
       </c>
       <c r="B32" t="n">
-        <v>79351</v>
+        <v>57950</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6434</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3918,10 +3914,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>759627</v>
+        <v>759567</v>
       </c>
       <c r="R32" t="n">
-        <v>7165400</v>
+        <v>7165410</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3956,13 +3952,17 @@
           <t>2026-04-17</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>hål hackat i gran</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 61033-2023 artfynd.xlsx
+++ b/artfynd/A 61033-2023 artfynd.xlsx
@@ -1411,38 +1411,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132612527</v>
+        <v>132613655</v>
       </c>
       <c r="B9" t="n">
-        <v>91868</v>
+        <v>80342</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>112</v>
+        <v>6456</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>759259</v>
+        <v>759705</v>
       </c>
       <c r="R9" t="n">
-        <v>7165528</v>
+        <v>7165475</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,6 +1489,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>på stammen av äldre asp</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1621,38 +1626,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132613655</v>
+        <v>132612527</v>
       </c>
       <c r="B11" t="n">
-        <v>80342</v>
+        <v>91868</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>112</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1663,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>759705</v>
+        <v>759259</v>
       </c>
       <c r="R11" t="n">
-        <v>7165475</v>
+        <v>7165528</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,11 +1704,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>på stammen av äldre asp</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1942,10 +1942,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132613364</v>
+        <v>132612240</v>
       </c>
       <c r="B14" t="n">
-        <v>57955</v>
+        <v>57958</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1953,16 +1953,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1973,11 +1973,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1985,10 +1981,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>759701</v>
+        <v>759575</v>
       </c>
       <c r="R14" t="n">
-        <v>7165535</v>
+        <v>7165402</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2025,14 +2021,14 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>hål hackat i basen på en gran</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG14" t="b">
         <v>0</v>
@@ -2052,10 +2048,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132612240</v>
+        <v>132613364</v>
       </c>
       <c r="B15" t="n">
-        <v>57958</v>
+        <v>57955</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2063,16 +2059,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2083,7 +2079,11 @@
       <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>759575</v>
+        <v>759701</v>
       </c>
       <c r="R15" t="n">
-        <v>7165402</v>
+        <v>7165535</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2131,14 +2131,14 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>hål hackat i basen på en gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="b">
         <v>0</v>
@@ -2585,10 +2585,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132613549</v>
+        <v>132613541</v>
       </c>
       <c r="B20" t="n">
-        <v>79333</v>
+        <v>83181</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2596,27 +2596,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -2690,10 +2690,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132613541</v>
+        <v>132613549</v>
       </c>
       <c r="B21" t="n">
-        <v>83181</v>
+        <v>79333</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2701,27 +2701,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -3656,42 +3656,41 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132612321</v>
+        <v>132611890</v>
       </c>
       <c r="B30" t="n">
-        <v>57955</v>
+        <v>79357</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6434</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3699,10 +3698,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>759567</v>
+        <v>759627</v>
       </c>
       <c r="R30" t="n">
-        <v>7165410</v>
+        <v>7165400</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3737,17 +3736,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>hål hackat i gran</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3766,7 +3761,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132613644</v>
+        <v>132612321</v>
       </c>
       <c r="B31" t="n">
         <v>57955</v>
@@ -3809,10 +3804,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>759714</v>
+        <v>759567</v>
       </c>
       <c r="R31" t="n">
-        <v>7165461</v>
+        <v>7165410</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3849,7 +3844,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>hål hackade i ihålig asp</t>
+          <t>hål hackat i gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3876,41 +3871,42 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132611890</v>
+        <v>132613644</v>
       </c>
       <c r="B32" t="n">
-        <v>79357</v>
+        <v>57955</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6434</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3918,10 +3914,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>759627</v>
+        <v>759714</v>
       </c>
       <c r="R32" t="n">
-        <v>7165400</v>
+        <v>7165461</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3956,13 +3952,17 @@
           <t>2026-04-17</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>hål hackade i ihålig asp</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 61033-2023 artfynd.xlsx
+++ b/artfynd/A 61033-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132500773</v>
+        <v>132612527</v>
       </c>
       <c r="B2" t="n">
-        <v>57955</v>
+        <v>91924</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,45 +686,44 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Storbrännan , Vb</t>
+          <t>Hambågamyran, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>759766</v>
+        <v>759259</v>
       </c>
       <c r="R2" t="n">
-        <v>7165494</v>
+        <v>7165528</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,12 +747,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,28 +761,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132500548</v>
+        <v>132612902</v>
       </c>
       <c r="B3" t="n">
-        <v>58119</v>
+        <v>79405</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,49 +791,44 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Storbrännan , Vb</t>
+          <t>Hambågamyran, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>759688</v>
+        <v>759375</v>
       </c>
       <c r="R3" t="n">
-        <v>7165497</v>
+        <v>7165650</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,12 +852,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -871,28 +866,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132500379</v>
+        <v>132613098</v>
       </c>
       <c r="B4" t="n">
-        <v>91939</v>
+        <v>91974</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,40 +896,44 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Storbrännan , Vb</t>
+          <t>Hambågamyran, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>759679</v>
+        <v>759358</v>
       </c>
       <c r="R4" t="n">
-        <v>7165533</v>
+        <v>7165706</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -957,12 +957,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -978,68 +978,67 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132500492</v>
+        <v>132613808</v>
       </c>
       <c r="B5" t="n">
-        <v>99130</v>
+        <v>91974</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Storbrännan , Vb</t>
+          <t>Hambågamyran, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>759732</v>
+        <v>759830</v>
       </c>
       <c r="R5" t="n">
-        <v>7165530</v>
+        <v>7165467</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1063,12 +1062,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1084,68 +1083,67 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132500598</v>
+        <v>132612134</v>
       </c>
       <c r="B6" t="n">
-        <v>57145</v>
+        <v>83222</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Storbrännan , Vb</t>
+          <t>Hambågamyran, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>759731</v>
+        <v>759624</v>
       </c>
       <c r="R6" t="n">
-        <v>7165465</v>
+        <v>7165409</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1169,12 +1167,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,28 +1181,29 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132500854</v>
+        <v>132612433</v>
       </c>
       <c r="B7" t="n">
-        <v>57955</v>
+        <v>83222</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1212,45 +1211,44 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Storbrännan , Vb</t>
+          <t>Hambågamyran, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>759725</v>
+        <v>759308</v>
       </c>
       <c r="R7" t="n">
-        <v>7165478</v>
+        <v>7165476</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1274,12 +1272,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1288,56 +1286,57 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132612503</v>
+        <v>132612652</v>
       </c>
       <c r="B8" t="n">
-        <v>79357</v>
+        <v>83222</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6434</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1348,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>759285</v>
+        <v>759276</v>
       </c>
       <c r="R8" t="n">
-        <v>7165516</v>
+        <v>7165633</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,38 +1410,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132613655</v>
+        <v>132612918</v>
       </c>
       <c r="B9" t="n">
-        <v>80342</v>
+        <v>83222</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1453,10 +1452,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>759705</v>
+        <v>759373</v>
       </c>
       <c r="R9" t="n">
-        <v>7165475</v>
+        <v>7165654</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,11 +1488,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>på stammen av äldre asp</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,10 +1515,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132612527</v>
+        <v>132612939</v>
       </c>
       <c r="B10" t="n">
-        <v>91868</v>
+        <v>83222</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1532,21 +1526,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>112</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1557,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>759259</v>
+        <v>759374</v>
       </c>
       <c r="R10" t="n">
-        <v>7165528</v>
+        <v>7165676</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1626,32 +1620,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132613335</v>
+        <v>132613541</v>
       </c>
       <c r="B11" t="n">
-        <v>91881</v>
+        <v>83222</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1668,10 +1662,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>759476</v>
+        <v>759750</v>
       </c>
       <c r="R11" t="n">
-        <v>7165646</v>
+        <v>7165501</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1731,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132612134</v>
+        <v>132500379</v>
       </c>
       <c r="B12" t="n">
-        <v>83181</v>
+        <v>91995</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1742,44 +1736,40 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hambågamyran, Vb</t>
+          <t>Storbrännan , Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>759624</v>
+        <v>759679</v>
       </c>
       <c r="R12" t="n">
-        <v>7165409</v>
+        <v>7165533</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1803,12 +1793,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1824,22 +1814,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132612190</v>
+        <v>132612369</v>
       </c>
       <c r="B13" t="n">
-        <v>57971</v>
+        <v>91995</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1847,27 +1837,30 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100048</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1875,10 +1868,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>759605</v>
+        <v>759530</v>
       </c>
       <c r="R13" t="n">
-        <v>7165415</v>
+        <v>7165474</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1913,17 +1906,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>påbörjat bohål?</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1942,42 +1931,41 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132613364</v>
+        <v>132613335</v>
       </c>
       <c r="B14" t="n">
-        <v>57955</v>
+        <v>91937</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1985,10 +1973,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>759701</v>
+        <v>759476</v>
       </c>
       <c r="R14" t="n">
-        <v>7165535</v>
+        <v>7165646</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2023,17 +2011,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>hål hackat i basen på en gran</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2052,38 +2036,41 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132612240</v>
+        <v>132612874</v>
       </c>
       <c r="B15" t="n">
-        <v>57958</v>
+        <v>79373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2091,10 +2078,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>759575</v>
+        <v>759375</v>
       </c>
       <c r="R15" t="n">
-        <v>7165402</v>
+        <v>7165650</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2129,17 +2116,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2158,42 +2141,41 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132612586</v>
+        <v>132612945</v>
       </c>
       <c r="B16" t="n">
-        <v>57958</v>
+        <v>79373</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2201,10 +2183,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>759275</v>
+        <v>759374</v>
       </c>
       <c r="R16" t="n">
-        <v>7165618</v>
+        <v>7165676</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2239,17 +2221,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2268,14 +2246,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132613617</v>
+        <v>132612971</v>
       </c>
       <c r="B17" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2310,10 +2288,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>759716</v>
+        <v>759371</v>
       </c>
       <c r="R17" t="n">
-        <v>7165500</v>
+        <v>7165678</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2373,38 +2351,41 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132613720</v>
+        <v>132613196</v>
       </c>
       <c r="B18" t="n">
-        <v>57958</v>
+        <v>79373</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2412,10 +2393,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>759791</v>
+        <v>759367</v>
       </c>
       <c r="R18" t="n">
-        <v>7165487</v>
+        <v>7165711</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2450,17 +2431,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2479,38 +2456,41 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132612091</v>
+        <v>132613549</v>
       </c>
       <c r="B19" t="n">
-        <v>57958</v>
+        <v>79373</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2518,10 +2498,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>759624</v>
+        <v>759750</v>
       </c>
       <c r="R19" t="n">
-        <v>7165409</v>
+        <v>7165501</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2556,17 +2536,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2585,14 +2561,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132613549</v>
+        <v>132613617</v>
       </c>
       <c r="B20" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2627,10 +2603,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>759750</v>
+        <v>759716</v>
       </c>
       <c r="R20" t="n">
-        <v>7165501</v>
+        <v>7165500</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2690,38 +2666,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132613541</v>
+        <v>132611890</v>
       </c>
       <c r="B21" t="n">
-        <v>83181</v>
+        <v>79397</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>6434</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -2732,10 +2708,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>759750</v>
+        <v>759627</v>
       </c>
       <c r="R21" t="n">
-        <v>7165501</v>
+        <v>7165400</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2795,42 +2771,41 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132613777</v>
+        <v>132612503</v>
       </c>
       <c r="B22" t="n">
-        <v>57955</v>
+        <v>79397</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6434</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2838,10 +2813,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>759822</v>
+        <v>759285</v>
       </c>
       <c r="R22" t="n">
-        <v>7165468</v>
+        <v>7165516</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2876,17 +2851,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>hål hackade i låga</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2905,42 +2876,41 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132613579</v>
+        <v>132612626</v>
       </c>
       <c r="B23" t="n">
-        <v>57955</v>
+        <v>79397</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6434</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2948,10 +2918,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>759771</v>
+        <v>759269</v>
       </c>
       <c r="R23" t="n">
-        <v>7165491</v>
+        <v>7165625</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2986,17 +2956,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>hack i död ved</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3015,38 +2981,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132613808</v>
+        <v>132613655</v>
       </c>
       <c r="B24" t="n">
-        <v>91918</v>
+        <v>80382</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -3057,10 +3023,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>759830</v>
+        <v>759705</v>
       </c>
       <c r="R24" t="n">
-        <v>7165467</v>
+        <v>7165475</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3093,6 +3059,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>på stammen av äldre asp</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3120,10 +3091,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132612369</v>
+        <v>132612190</v>
       </c>
       <c r="B25" t="n">
-        <v>91939</v>
+        <v>57988</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3131,30 +3102,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5442</v>
+        <v>100048</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3162,10 +3130,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>759530</v>
+        <v>759605</v>
       </c>
       <c r="R25" t="n">
-        <v>7165474</v>
+        <v>7165415</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3200,13 +3168,17 @@
           <t>2026-04-17</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>påbörjat bohål?</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF25" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3225,10 +3197,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132612549</v>
+        <v>132613674</v>
       </c>
       <c r="B26" t="n">
-        <v>57955</v>
+        <v>57988</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3236,16 +3208,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3256,11 +3228,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3268,10 +3236,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>759273</v>
+        <v>759705</v>
       </c>
       <c r="R26" t="n">
-        <v>7165552</v>
+        <v>7165475</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3308,14 +3276,14 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>hål hackat i träd</t>
+          <t>påbörjat litet bohål i asp</t>
         </is>
       </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG26" t="b">
         <v>0</v>
@@ -3335,14 +3303,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132613756</v>
+        <v>132500773</v>
       </c>
       <c r="B27" t="n">
-        <v>57955</v>
+        <v>57972</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3374,17 +3342,17 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Hambågamyran, Vb</t>
+          <t>Storbrännan , Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>759795</v>
+        <v>759766</v>
       </c>
       <c r="R27" t="n">
-        <v>7165475</v>
+        <v>7165494</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3408,17 +3376,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>många hål hackade i gran</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3433,39 +3396,39 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132613674</v>
+        <v>132500854</v>
       </c>
       <c r="B28" t="n">
-        <v>57971</v>
+        <v>57972</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100048</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3473,24 +3436,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hambågamyran, Vb</t>
+          <t>Storbrännan , Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>759705</v>
+        <v>759725</v>
       </c>
       <c r="R28" t="n">
-        <v>7165475</v>
+        <v>7165478</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3514,24 +3481,19 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>påbörjat litet bohål i asp</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="b">
         <v>0</v>
@@ -3539,22 +3501,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132611890</v>
+        <v>132612321</v>
       </c>
       <c r="B29" t="n">
-        <v>79357</v>
+        <v>57972</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3562,30 +3524,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6434</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3593,10 +3556,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>759627</v>
+        <v>759567</v>
       </c>
       <c r="R29" t="n">
-        <v>7165400</v>
+        <v>7165410</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3631,13 +3594,17 @@
           <t>2026-04-17</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>hål hackat i gran</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3656,14 +3623,14 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132613644</v>
+        <v>132612549</v>
       </c>
       <c r="B30" t="n">
-        <v>57955</v>
+        <v>57972</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3699,10 +3666,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>759714</v>
+        <v>759273</v>
       </c>
       <c r="R30" t="n">
-        <v>7165461</v>
+        <v>7165552</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3739,7 +3706,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>hål hackade i ihålig asp</t>
+          <t>hål hackat i träd</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3766,14 +3733,14 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132612321</v>
+        <v>132612772</v>
       </c>
       <c r="B31" t="n">
-        <v>57955</v>
+        <v>57972</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -3809,10 +3776,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>759567</v>
+        <v>759382</v>
       </c>
       <c r="R31" t="n">
-        <v>7165410</v>
+        <v>7165639</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3849,7 +3816,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>hål hackat i gran</t>
+          <t>hål hackat i träd</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3876,41 +3843,42 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132612433</v>
+        <v>132613364</v>
       </c>
       <c r="B32" t="n">
-        <v>83181</v>
+        <v>57972</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3918,10 +3886,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>759308</v>
+        <v>759701</v>
       </c>
       <c r="R32" t="n">
-        <v>7165476</v>
+        <v>7165535</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3956,13 +3924,17 @@
           <t>2026-04-17</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>hål hackat i basen på en gran</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3981,27 +3953,27 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132611969</v>
+        <v>132613579</v>
       </c>
       <c r="B33" t="n">
-        <v>57958</v>
+        <v>57972</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4012,7 +3984,11 @@
       <c r="I33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4020,10 +3996,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>759627</v>
+        <v>759771</v>
       </c>
       <c r="R33" t="n">
-        <v>7165400</v>
+        <v>7165491</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4060,14 +4036,14 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>hack i död ved</t>
         </is>
       </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="b">
         <v>0</v>
@@ -4084,6 +4060,1296 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>132613644</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Hambågamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>759714</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7165461</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>hål hackade i ihålig asp</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>132613756</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Hambågamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>759795</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7165475</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>många hål hackade i gran</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>132613777</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Hambågamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>759822</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7165468</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>hål hackade i låga</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>132611969</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Hambågamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>759627</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7165400</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>132612091</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Hambågamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>759624</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7165409</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>132612240</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Hambågamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>759575</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7165402</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>132612586</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Hambågamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>759275</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7165618</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>132613293</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Hambågamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>759388</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7165671</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>132613720</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Hambågamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>759791</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7165487</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>132500598</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Storbrännan , Vb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>759731</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7165465</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>132500548</v>
+      </c>
+      <c r="B44" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Storbrännan , Vb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>759688</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7165497</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>132500492</v>
+      </c>
+      <c r="B45" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Storbrännan , Vb</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>759732</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7165530</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61033-2023 artfynd.xlsx
+++ b/artfynd/A 61033-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AZ45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132612527</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132612902</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132613098</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132613808</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132612134</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1302,6 +1332,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132612433</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1407,6 +1442,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132612652</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1512,6 +1552,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132612918</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1617,6 +1662,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132612939</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1722,6 +1772,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132613541</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1823,6 +1878,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132500379</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1928,6 +1988,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132612369</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2033,6 +2098,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132613335</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2138,6 +2208,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132612874</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2243,6 +2318,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132612945</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2348,6 +2428,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132612971</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2453,6 +2538,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132613196</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2558,6 +2648,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132613549</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2663,6 +2758,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132613617</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2768,6 +2868,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132611890</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2873,6 +2978,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132612503</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2978,6 +3088,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132612626</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3088,6 +3203,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132613655</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3194,6 +3314,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132612190</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3300,6 +3425,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132613674</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3405,6 +3535,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132500773</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3510,6 +3645,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132500854</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3620,6 +3760,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132612321</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3730,6 +3875,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132612549</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3840,6 +3990,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132612772</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3950,6 +4105,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132613364</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4060,6 +4220,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132613579</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4170,6 +4335,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132613644</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4280,6 +4450,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132613756</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4390,6 +4565,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132613777</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4496,6 +4676,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132611969</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4602,6 +4787,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132612091</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4708,6 +4898,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132612240</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4818,6 +5013,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132612586</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4924,6 +5124,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132613293</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5030,6 +5235,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132613720</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5135,6 +5345,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132500598</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5244,6 +5459,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132500548</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5350,8 +5570,59 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132500492</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>